--- a/diseases/d144/2005-2009.xlsx
+++ b/diseases/d144/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2397,9 +2388,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2941,9 +2929,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3485,9 +3470,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4029,9 +4011,6 @@
       <c r="O20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -4573,9 +4552,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5117,9 +5093,6 @@
       <c r="O26" t="n">
         <v>2</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -5661,9 +5634,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6205,9 +6175,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6749,9 +6716,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7293,9 +7257,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -7837,9 +7798,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8233,9 +8191,6 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -8777,9 +8732,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -9321,9 +9273,6 @@
       <c r="O49" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -9865,9 +9814,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10409,9 +10355,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -10953,9 +10896,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11645,9 +11585,6 @@
       <c r="O62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.04291390569325913</v>
       </c>
@@ -12189,9 +12126,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12733,9 +12667,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13277,9 +13208,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -13821,9 +13749,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -14365,9 +14290,6 @@
       <c r="O77" t="n">
         <v>0</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0</v>
       </c>
@@ -15057,9 +14979,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -15453,9 +15372,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -15997,9 +15913,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -16689,9 +16602,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -17381,9 +17291,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -18073,9 +17980,6 @@
       <c r="O98" t="n">
         <v>2</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -18765,9 +18669,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -19457,9 +19358,6 @@
       <c r="O106" t="n">
         <v>1</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -20149,9 +20047,6 @@
       <c r="O110" t="n">
         <v>0</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0</v>
       </c>
@@ -20841,9 +20736,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -21533,9 +21425,6 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.02123588609920132</v>
       </c>
@@ -22225,9 +22114,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -22917,9 +22803,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -23609,9 +23492,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -24005,9 +23885,6 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -24697,9 +24574,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -25389,9 +25263,6 @@
       <c r="O140" t="n">
         <v>0</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0</v>
       </c>
@@ -26081,9 +25952,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -26773,9 +26641,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -27465,9 +27330,6 @@
       <c r="O152" t="n">
         <v>1</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -28305,9 +28167,6 @@
       <c r="O157" t="n">
         <v>0</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
@@ -29145,9 +29004,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -29985,9 +29841,6 @@
       <c r="O167" t="n">
         <v>1</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -30825,9 +30678,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -31665,9 +31515,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -32505,9 +32352,6 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -33345,9 +33189,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -33741,9 +33582,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -34581,9 +34419,6 @@
       <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0</v>
       </c>
@@ -35421,9 +35256,6 @@
       <c r="O199" t="n">
         <v>0</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0</v>
       </c>
@@ -36261,9 +36093,6 @@
       <c r="O204" t="n">
         <v>0</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0</v>
       </c>
@@ -37101,9 +36930,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -37941,9 +37767,6 @@
       <c r="O214" t="n">
         <v>1</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -38781,9 +38604,6 @@
       <c r="O219" t="n">
         <v>0</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0</v>
       </c>
@@ -39621,9 +39441,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -40461,9 +40278,6 @@
       <c r="O229" t="n">
         <v>1</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -41301,9 +41115,6 @@
       <c r="O234" t="n">
         <v>2</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -42289,9 +42100,6 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -43127,9 +42935,6 @@
         <v>0</v>
       </c>
       <c r="O245" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q245" t="n">
         <v>0</v>
       </c>
       <c r="R245" t="n">
